--- a/src/excel-data/tohoku.xlsx
+++ b/src/excel-data/tohoku.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/Cao Yuxuan/テストweb/findmyrailpass.net/src/excel-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{043A0D93-CE42-9B4F-9EC6-DA4452F01265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F02D95BB-843F-8642-A02C-B45CD2509C70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="东北周游券" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="286">
   <si>
     <t>sortOrder</t>
   </si>
@@ -313,12 +313,6 @@
   </si>
   <si>
     <t>https://www.akita-nairiku.com/ticket/</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>全線タイプ　大人：2,500円／小人：1,250円
-Ａタイプ　　大人：1,500円／小人： 750円
-Ｂタイプ　　大人：1,500円／小人： 750円</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -676,9 +670,6 @@
   </si>
   <si>
     <t>青森1日周游券</t>
-  </si>
-  <si>
-    <t>秋田内陆1日周游券</t>
   </si>
   <si>
     <t>生日1日周游券</t>
@@ -1419,6 +1410,62 @@
   </si>
   <si>
     <t>【利用期間】周末假日以及8月1日～4日,12月30日～1月3日</t>
+  </si>
+  <si>
+    <t>秋田内陆1日周游券（全部）</t>
+    <rPh sb="10" eb="11">
+      <t>quan bu</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>秋田内陆1日周游券（typeA）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>秋田内陆1日周游券（typeB）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>akita-nairikku-1day-pass-a</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>akita-nairikku-1day-pass-b</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/images/coverage/akita-nairikku-1day-pass-a.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/images/coverage/akita-nairikku-1day-pass-b.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※指定席需要预约，一等座需要加钱</t>
+    <rPh sb="1" eb="2">
+      <t>zhi ding xi</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>xu yao</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>yu yue</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>yi deng z</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>xu yao</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>jia q</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>qian</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1875,7 +1922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF152"/>
+  <dimension ref="A1:AF154"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="6"/>
@@ -1913,7 +1960,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>3</v>
@@ -1988,7 +2035,7 @@
         <v>81</v>
       </c>
       <c r="AF1" s="8" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="1:32" s="1" customFormat="1">
@@ -1999,10 +2046,10 @@
         <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E2" s="1">
         <v>3880</v>
@@ -2023,7 +2070,7 @@
         <v>24</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>25</v>
@@ -2038,7 +2085,7 @@
         <v>26</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>27</v>
@@ -2047,7 +2094,7 @@
         <v>28</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="W2" s="2" t="s">
         <v>83</v>
@@ -2065,10 +2112,10 @@
         <v>24</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AF2" s="9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:32" s="1" customFormat="1">
@@ -2079,10 +2126,10 @@
         <v>30</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E3" s="1">
         <v>2720</v>
@@ -2097,7 +2144,7 @@
         <v>24</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>25</v>
@@ -2112,7 +2159,7 @@
         <v>26</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>31</v>
@@ -2121,7 +2168,7 @@
         <v>28</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="W3" s="2" t="s">
         <v>82</v>
@@ -2139,10 +2186,10 @@
         <v>24</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AF3" s="9" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:32" s="1" customFormat="1" ht="64">
@@ -2153,10 +2200,10 @@
         <v>32</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E4" s="1">
         <v>2720</v>
@@ -2171,7 +2218,7 @@
         <v>24</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="O4" s="1">
         <v>1</v>
@@ -2183,10 +2230,10 @@
         <v>24</v>
       </c>
       <c r="R4" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="S4" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>129</v>
       </c>
       <c r="T4" s="1" t="s">
         <v>33</v>
@@ -2213,10 +2260,10 @@
         <v>1</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AF4" s="9" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:32" s="1" customFormat="1" ht="64">
@@ -2227,10 +2274,10 @@
         <v>35</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E5" s="1">
         <v>2510</v>
@@ -2245,7 +2292,7 @@
         <v>24</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O5" s="1">
         <v>1</v>
@@ -2257,10 +2304,10 @@
         <v>24</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T5" s="1" t="s">
         <v>36</v>
@@ -2287,10 +2334,10 @@
         <v>1</v>
       </c>
       <c r="AB5" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AF5" s="9" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="1:32" s="1" customFormat="1" ht="64">
@@ -2301,10 +2348,10 @@
         <v>37</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E6" s="1">
         <v>2520</v>
@@ -2319,7 +2366,7 @@
         <v>24</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O6" s="1">
         <v>1</v>
@@ -2334,7 +2381,7 @@
         <v>26</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="T6" s="1" t="s">
         <v>38</v>
@@ -2343,7 +2390,7 @@
         <v>28</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="W6" s="2" t="s">
         <v>87</v>
@@ -2361,10 +2408,10 @@
         <v>1</v>
       </c>
       <c r="AB6" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AF6" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="1:32" s="1" customFormat="1">
@@ -2372,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E7" s="1">
         <v>1000</v>
@@ -2393,7 +2440,7 @@
         <v>24</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O7" s="1">
         <v>1</v>
@@ -2408,10 +2455,10 @@
         <v>26</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="U7" s="1" t="s">
         <v>28</v>
@@ -2435,7 +2482,7 @@
         <v>24</v>
       </c>
       <c r="AF7" s="9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="1:32" s="1" customFormat="1" ht="80">
@@ -2443,13 +2490,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E8" s="1">
         <v>2100</v>
@@ -2467,7 +2514,7 @@
         <v>1530</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="O8" s="1">
         <v>1</v>
@@ -2479,13 +2526,13 @@
         <v>24</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="U8" s="1" t="s">
         <v>28</v>
@@ -2509,13 +2556,13 @@
         <v>1</v>
       </c>
       <c r="AB8" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AF8" s="9" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" s="1" customFormat="1" ht="144">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" s="1" customFormat="1">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -2523,10 +2570,10 @@
         <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>170</v>
+        <v>278</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E9" s="1">
         <v>2500</v>
@@ -2540,11 +2587,9 @@
       <c r="H9" s="1">
         <v>1200</v>
       </c>
-      <c r="M9" s="4" t="s">
-        <v>93</v>
-      </c>
+      <c r="M9" s="4"/>
       <c r="N9" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="O9" s="1">
         <v>1</v>
@@ -2559,7 +2604,7 @@
         <v>26</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T9" s="1" t="s">
         <v>42</v>
@@ -2568,13 +2613,13 @@
         <v>28</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="W9" s="2" t="s">
         <v>92</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y9" s="1" t="s">
         <v>29</v>
@@ -2586,39 +2631,34 @@
         <v>24</v>
       </c>
       <c r="AF9" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="1:32" s="1" customFormat="1">
       <c r="A10" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>41</v>
+        <v>281</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>179</v>
+        <v>279</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="E10" s="1">
-        <v>3500</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>24</v>
+        <v>1500</v>
       </c>
       <c r="G10" s="1">
-        <v>1750</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>24</v>
-      </c>
+        <v>750</v>
+      </c>
+      <c r="M10" s="4"/>
       <c r="N10" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>25</v>
+        <v>231</v>
+      </c>
+      <c r="O10" s="1">
+        <v>1</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>24</v>
@@ -2630,22 +2670,22 @@
         <v>26</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>43</v>
+        <v>283</v>
       </c>
       <c r="U10" s="1" t="s">
         <v>28</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="W10" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="X10" s="1" t="s">
-        <v>24</v>
+      <c r="X10" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="Y10" s="1" t="s">
         <v>29</v>
@@ -2656,40 +2696,32 @@
       <c r="AA10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AB10" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="AF10" s="9" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" s="1" customFormat="1" ht="128">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" s="1" customFormat="1">
       <c r="A11" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>97</v>
+        <v>282</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>171</v>
+        <v>280</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="E11" s="1">
         <v>1500</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="G11" s="1">
         <v>750</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>24</v>
-      </c>
+      <c r="M11" s="4"/>
       <c r="N11" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="O11" s="1">
         <v>1</v>
@@ -2704,69 +2736,66 @@
         <v>26</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>98</v>
+        <v>284</v>
       </c>
       <c r="U11" s="1" t="s">
         <v>28</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>39</v>
+        <v>135</v>
       </c>
       <c r="W11" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="X11" s="1" t="s">
-        <v>24</v>
+      <c r="X11" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="Y11" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Z11" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AB11" s="4" t="s">
-        <v>227</v>
-      </c>
       <c r="AF11" s="9" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" s="1" customFormat="1" ht="16">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" s="1" customFormat="1">
       <c r="A12" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E12" s="1">
-        <v>1480</v>
+        <v>3500</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G12" s="1">
-        <v>900</v>
+        <v>1750</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>24</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="O12" s="1">
-        <v>1</v>
+        <v>232</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>24</v>
@@ -2778,19 +2807,19 @@
         <v>26</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="U12" s="1" t="s">
         <v>28</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="X12" s="1" t="s">
         <v>24</v>
@@ -2799,45 +2828,45 @@
         <v>29</v>
       </c>
       <c r="Z12" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AB12" s="4" t="s">
-        <v>105</v>
+      <c r="AB12" s="1" t="s">
+        <v>226</v>
       </c>
       <c r="AF12" s="9" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" s="1" customFormat="1" ht="48">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" s="1" customFormat="1" ht="128">
       <c r="A13" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="E13" s="1">
-        <v>1100</v>
+        <v>1500</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G13" s="1">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>24</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="O13" s="1">
         <v>1</v>
@@ -2849,13 +2878,13 @@
         <v>24</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>128</v>
+        <v>26</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="U13" s="1" t="s">
         <v>28</v>
@@ -2864,7 +2893,7 @@
         <v>39</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="X13" s="1" t="s">
         <v>24</v>
@@ -2873,45 +2902,45 @@
         <v>29</v>
       </c>
       <c r="Z13" s="1">
-        <v>3</v>
-      </c>
-      <c r="AA13" s="1" t="b">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="AA13" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="AB13" s="4" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="AF13" s="9" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32" s="1" customFormat="1" ht="32">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" s="1" customFormat="1" ht="16">
       <c r="A14" s="1">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E14" s="1">
-        <v>3000</v>
+        <v>1480</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G14" s="1">
-        <v>1500</v>
+        <v>900</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>24</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>24</v>
+        <v>233</v>
       </c>
       <c r="O14" s="1">
         <v>1</v>
@@ -2923,25 +2952,25 @@
         <v>24</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>128</v>
+        <v>26</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="U14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>39</v>
+        <v>136</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="X14" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
+      </c>
+      <c r="X14" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="Y14" s="1" t="s">
         <v>29</v>
@@ -2949,47 +2978,47 @@
       <c r="Z14" s="1">
         <v>4</v>
       </c>
-      <c r="AA14" s="1" t="b">
+      <c r="AA14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB14" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="AF14" s="9" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" s="1" customFormat="1" ht="48">
+      <c r="A15" s="1">
+        <v>12</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1100</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" s="1">
+        <v>500</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="O15" s="1">
         <v>1</v>
       </c>
-      <c r="AB14" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="AF14" s="9" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" s="1" customFormat="1">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E15" s="1">
-        <v>6100</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G15" s="1">
-        <v>3050</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="P15" s="1" t="s">
         <v>24</v>
       </c>
@@ -2997,13 +3026,13 @@
         <v>24</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="U15" s="1" t="s">
         <v>28</v>
@@ -3012,10 +3041,10 @@
         <v>39</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="X15" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
+      </c>
+      <c r="X15" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="Y15" s="1" t="s">
         <v>29</v>
@@ -3023,42 +3052,45 @@
       <c r="Z15" s="1">
         <v>3</v>
       </c>
-      <c r="AA15" s="1" t="s">
-        <v>24</v>
+      <c r="AA15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="4" t="s">
+        <v>276</v>
       </c>
       <c r="AF15" s="9" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32" s="1" customFormat="1" ht="16">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" s="1" customFormat="1" ht="32">
       <c r="A16" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>199</v>
+        <v>148</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E16" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="1">
         <v>1500</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G16" s="1">
-        <v>750</v>
-      </c>
       <c r="H16" s="1" t="s">
         <v>24</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="O16" s="10">
+        <v>24</v>
+      </c>
+      <c r="O16" s="1">
         <v>1</v>
       </c>
       <c r="P16" s="1" t="s">
@@ -3068,13 +3100,13 @@
         <v>24</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="U16" s="1" t="s">
         <v>28</v>
@@ -3083,54 +3115,57 @@
         <v>39</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="Y16" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Z16" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA16" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="AB16" s="4" t="s">
+        <v>277</v>
+      </c>
       <c r="AF16" s="9" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17" spans="1:32" s="1" customFormat="1">
       <c r="A17" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>202</v>
+        <v>149</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="E17" s="1">
-        <v>2400</v>
+        <v>6100</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G17" s="1">
-        <v>1200</v>
+        <v>3050</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>24</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="O17" s="1">
-        <v>1</v>
+        <v>234</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="P17" s="1" t="s">
         <v>24</v>
@@ -3139,13 +3174,13 @@
         <v>24</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>128</v>
+        <v>26</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="U17" s="1" t="s">
         <v>28</v>
@@ -3154,10 +3189,10 @@
         <v>39</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Y17" s="1" t="s">
         <v>29</v>
@@ -3165,55 +3200,58 @@
       <c r="Z17" s="1">
         <v>3</v>
       </c>
-      <c r="AA17" s="1" t="b">
-        <v>1</v>
+      <c r="AA17" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="AF17" s="9" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="18" spans="1:32" s="1" customFormat="1" ht="16">
       <c r="A18" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="E18" s="1">
-        <v>2600</v>
+        <v>1500</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G18" s="1">
-        <v>1300</v>
+        <v>750</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>24</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="O18" s="1">
+        <v>235</v>
+      </c>
+      <c r="O18" s="10">
         <v>1</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="Q18" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="R18" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>52</v>
+        <v>123</v>
       </c>
       <c r="U18" s="1" t="s">
         <v>28</v>
@@ -3222,10 +3260,10 @@
         <v>39</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Y18" s="1" t="s">
         <v>29</v>
@@ -3237,36 +3275,36 @@
         <v>1</v>
       </c>
       <c r="AF18" s="9" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="19" spans="1:32" s="1" customFormat="1">
       <c r="A19" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>151</v>
+        <v>200</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E19" s="1">
-        <v>1000</v>
+        <v>2400</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>24</v>
+      <c r="G19" s="1">
+        <v>1200</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>24</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="O19" s="1">
         <v>1</v>
@@ -3278,13 +3316,13 @@
         <v>24</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>54</v>
+        <v>127</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="U19" s="1" t="s">
         <v>28</v>
@@ -3293,56 +3331,51 @@
         <v>39</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Y19" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Z19" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA19" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="AB19" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="AF19" s="9" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="20" spans="1:32" s="1" customFormat="1">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" s="1" customFormat="1" ht="16">
       <c r="A20" s="1">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="E20" s="1">
-        <v>1000</v>
+        <v>2600</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>24</v>
+      <c r="G20" s="1">
+        <v>1300</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
       <c r="N20" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="O20" s="1">
         <v>1</v>
@@ -3350,17 +3383,14 @@
       <c r="P20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Q20" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="R20" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="U20" s="1" t="s">
         <v>28</v>
@@ -3369,51 +3399,51 @@
         <v>39</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="Y20" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Z20" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA20" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="AB20" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="AF20" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="21" spans="1:32" s="1" customFormat="1">
       <c r="A21" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="E21" s="1">
-        <v>840</v>
-      </c>
-      <c r="G21" s="1">
-        <v>420</v>
-      </c>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
+        <v>1000</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="N21" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="O21" s="1">
         <v>1</v>
@@ -3428,10 +3458,10 @@
         <v>54</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="U21" s="1" t="s">
         <v>28</v>
@@ -3440,48 +3470,56 @@
         <v>39</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="X21" s="1" t="s">
-        <v>24</v>
+        <v>112</v>
+      </c>
+      <c r="X21" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>146</v>
+        <v>29</v>
       </c>
       <c r="Z21" s="1">
-        <v>5</v>
-      </c>
-      <c r="AA21" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
+      </c>
+      <c r="AA21" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="1" t="s">
+        <v>239</v>
       </c>
       <c r="AF21" s="9" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="22" spans="1:32" s="1" customFormat="1" ht="16">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" s="1" customFormat="1">
       <c r="A22" s="1">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="E22" s="1">
-        <v>620</v>
-      </c>
-      <c r="G22" s="1">
-        <v>310</v>
+        <v>1000</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
       <c r="N22" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="O22" s="1">
         <v>1</v>
@@ -3489,14 +3527,17 @@
       <c r="P22" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="Q22" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="R22" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="U22" s="1" t="s">
         <v>28</v>
@@ -3505,54 +3546,51 @@
         <v>39</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="X22" s="1" t="s">
-        <v>24</v>
+        <v>112</v>
+      </c>
+      <c r="X22" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="Y22" s="1" t="s">
-        <v>146</v>
+        <v>29</v>
       </c>
       <c r="Z22" s="1">
-        <v>5</v>
-      </c>
-      <c r="AA22" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
+      </c>
+      <c r="AA22" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="1" t="s">
+        <v>240</v>
       </c>
       <c r="AF22" s="9" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="23" spans="1:32" s="1" customFormat="1">
       <c r="A23" s="1">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E23" s="1">
-        <v>920</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>24</v>
+        <v>840</v>
       </c>
       <c r="G23" s="1">
-        <v>460</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>24</v>
+        <v>420</v>
       </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O23" s="1">
         <v>1</v>
@@ -3564,13 +3602,13 @@
         <v>24</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>128</v>
+        <v>54</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="U23" s="1" t="s">
         <v>28</v>
@@ -3579,54 +3617,48 @@
         <v>39</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="X23" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
+      </c>
+      <c r="X23" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Z23" s="1">
         <v>5</v>
       </c>
-      <c r="AA23" s="1" t="b">
-        <v>1</v>
+      <c r="AA23" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="AF23" s="9" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="24" spans="1:32" s="1" customFormat="1">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" s="1" customFormat="1" ht="16">
       <c r="A24" s="1">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>206</v>
+        <v>180</v>
       </c>
       <c r="E24" s="1">
-        <v>1500</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>24</v>
+        <v>620</v>
       </c>
       <c r="G24" s="1">
-        <v>750</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>24</v>
+        <v>310</v>
       </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
       <c r="N24" s="1" t="s">
-        <v>153</v>
+        <v>237</v>
       </c>
       <c r="O24" s="1">
         <v>1</v>
@@ -3634,17 +3666,14 @@
       <c r="P24" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Q24" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="R24" s="1" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="U24" s="1" t="s">
         <v>28</v>
@@ -3653,48 +3682,45 @@
         <v>39</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="X24" s="1" t="s">
         <v>24</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="Z24" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA24" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AB24" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="AF24" s="9" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="25" spans="1:32" s="1" customFormat="1">
       <c r="A25" s="1">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E25" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G25" s="1">
-        <v>300</v>
+        <v>460</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>24</v>
@@ -3703,7 +3729,7 @@
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
       <c r="N25" s="1" t="s">
-        <v>155</v>
+        <v>238</v>
       </c>
       <c r="O25" s="1">
         <v>1</v>
@@ -3715,13 +3741,13 @@
         <v>24</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="U25" s="1" t="s">
         <v>28</v>
@@ -3730,48 +3756,45 @@
         <v>39</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="X25" s="1" t="s">
-        <v>24</v>
+        <v>114</v>
+      </c>
+      <c r="X25" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="Z25" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA25" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="AB25" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="AF25" s="9" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="26" spans="1:32" s="1" customFormat="1">
       <c r="A26" s="1">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E26" s="1">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G26" s="1">
-        <v>450</v>
+        <v>750</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>24</v>
@@ -3780,7 +3803,7 @@
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O26" s="1">
         <v>1</v>
@@ -3792,13 +3815,13 @@
         <v>24</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>121</v>
+        <v>26</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="U26" s="1" t="s">
         <v>28</v>
@@ -3807,7 +3830,7 @@
         <v>39</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="X26" s="1" t="s">
         <v>24</v>
@@ -3818,37 +3841,37 @@
       <c r="Z26" s="1">
         <v>3</v>
       </c>
-      <c r="AA26" s="1" t="b">
-        <v>1</v>
+      <c r="AA26" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="AB26" s="1" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="AF26" s="9" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="27" spans="1:32" s="1" customFormat="1" ht="64">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="27" spans="1:32" s="1" customFormat="1">
       <c r="A27" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E27" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>24</v>
+      <c r="G27" s="1">
+        <v>300</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>24</v>
@@ -3857,7 +3880,7 @@
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
       <c r="N27" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O27" s="1">
         <v>1</v>
@@ -3872,10 +3895,10 @@
         <v>26</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="U27" s="1" t="s">
         <v>28</v>
@@ -3883,8 +3906,8 @@
       <c r="V27" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="W27" s="1" t="s">
-        <v>24</v>
+      <c r="W27" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="X27" s="1" t="s">
         <v>24</v>
@@ -3893,39 +3916,39 @@
         <v>29</v>
       </c>
       <c r="Z27" s="1">
-        <v>5</v>
-      </c>
-      <c r="AA27" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB27" s="4" t="s">
-        <v>122</v>
+        <v>3</v>
+      </c>
+      <c r="AA27" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB27" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="AF27" s="9" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="28" spans="1:32" s="1" customFormat="1">
       <c r="A28" s="1">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E28" s="1">
-        <v>1300</v>
+        <v>900</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G28" s="1">
-        <v>650</v>
+        <v>450</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>24</v>
@@ -3934,7 +3957,7 @@
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
       <c r="N28" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="O28" s="1">
         <v>1</v>
@@ -3946,13 +3969,13 @@
         <v>24</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="U28" s="1" t="s">
         <v>28</v>
@@ -3961,7 +3984,7 @@
         <v>39</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="X28" s="1" t="s">
         <v>24</v>
@@ -3970,33 +3993,33 @@
         <v>29</v>
       </c>
       <c r="Z28" s="1">
-        <v>4</v>
-      </c>
-      <c r="AA28" s="1" t="s">
-        <v>24</v>
+        <v>3</v>
+      </c>
+      <c r="AA28" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="AB28" s="1" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="AF28" s="9" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="29" spans="1:32" s="1" customFormat="1">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="29" spans="1:32" s="1" customFormat="1" ht="64">
       <c r="A29" s="1">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E29" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>24</v>
@@ -4011,7 +4034,7 @@
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
       <c r="N29" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="O29" s="1">
         <v>1</v>
@@ -4026,10 +4049,10 @@
         <v>26</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U29" s="1" t="s">
         <v>28</v>
@@ -4037,8 +4060,8 @@
       <c r="V29" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="W29" s="2" t="s">
-        <v>118</v>
+      <c r="W29" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="X29" s="1" t="s">
         <v>24</v>
@@ -4047,39 +4070,39 @@
         <v>29</v>
       </c>
       <c r="Z29" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AB29" s="1" t="s">
-        <v>144</v>
+      <c r="AB29" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="AF29" s="9" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="30" spans="1:32" s="1" customFormat="1">
       <c r="A30" s="1">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="E30" s="1">
-        <v>5150</v>
+        <v>1300</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G30" s="1">
-        <v>2610</v>
+        <v>650</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>24</v>
@@ -4088,10 +4111,10 @@
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
       <c r="N30" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O30" s="1" t="s">
-        <v>25</v>
+        <v>157</v>
+      </c>
+      <c r="O30" s="1">
+        <v>1</v>
       </c>
       <c r="P30" s="1" t="s">
         <v>24</v>
@@ -4103,10 +4126,10 @@
         <v>26</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="U30" s="1" t="s">
         <v>28</v>
@@ -4115,7 +4138,7 @@
         <v>39</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="X30" s="1" t="s">
         <v>24</v>
@@ -4124,36 +4147,39 @@
         <v>29</v>
       </c>
       <c r="Z30" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA30" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="AB30" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="AF30" s="9" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="31" spans="1:32" s="1" customFormat="1" ht="16">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="31" spans="1:32" s="1" customFormat="1">
       <c r="A31" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E31" s="1">
-        <v>4190</v>
+        <v>1500</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G31" s="1">
-        <v>2130</v>
+      <c r="G31" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>24</v>
@@ -4162,10 +4188,10 @@
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
       <c r="N31" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O31" s="1" t="s">
-        <v>25</v>
+        <v>157</v>
+      </c>
+      <c r="O31" s="1">
+        <v>1</v>
       </c>
       <c r="P31" s="1" t="s">
         <v>24</v>
@@ -4177,10 +4203,10 @@
         <v>26</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="U31" s="1" t="s">
         <v>28</v>
@@ -4189,7 +4215,7 @@
         <v>39</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="X31" s="1" t="s">
         <v>24</v>
@@ -4203,130 +4229,277 @@
       <c r="AA31" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="AB31" s="1" t="s">
+        <v>143</v>
+      </c>
       <c r="AF31" s="9" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="32" spans="1:32" s="1" customFormat="1">
       <c r="A32" s="1">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>213</v>
+        <v>74</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>215</v>
+        <v>159</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="E32" s="1">
-        <v>30000</v>
+        <v>5150</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G32" s="1">
-        <v>15000</v>
-      </c>
+        <v>2610</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
       <c r="N32" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="O32" s="1">
-        <v>5</v>
+        <v>222</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="S32" s="1" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>218</v>
+        <v>75</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>220</v>
+        <v>28</v>
       </c>
       <c r="V32" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="W32" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="X32" s="7" t="s">
-        <v>223</v>
+        <v>39</v>
+      </c>
+      <c r="W32" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="X32" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="Y32" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Z32" s="1">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="AA32" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="AF32" s="9" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="33" spans="1:32" s="1" customFormat="1">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="33" spans="1:32" s="1" customFormat="1" ht="16">
       <c r="A33" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>214</v>
+        <v>76</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>216</v>
+        <v>160</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="E33" s="1">
-        <v>48000</v>
+        <v>4190</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G33" s="1">
-        <v>24000</v>
-      </c>
+        <v>2130</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
       <c r="N33" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="O33" s="1">
-        <v>10</v>
+        <v>222</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="R33" s="1" t="s">
         <v>26</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>217</v>
+        <v>77</v>
       </c>
       <c r="U33" s="1" t="s">
-        <v>220</v>
+        <v>28</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="W33" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="X33" s="7" t="s">
-        <v>223</v>
+        <v>39</v>
+      </c>
+      <c r="W33" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="X33" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="Y33" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Z33" s="1">
+        <v>3</v>
+      </c>
+      <c r="AA33" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF33" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="34" spans="1:32" s="1" customFormat="1">
+      <c r="A34" s="1">
+        <v>31</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E34" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G34" s="1">
+        <v>15000</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="O34" s="1">
         <v>5</v>
       </c>
-      <c r="AF33" s="9" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="97" spans="11:13">
-      <c r="K97" s="5"/>
-      <c r="L97" s="5"/>
-      <c r="M97" s="5"/>
-    </row>
-    <row r="98" spans="11:13">
-      <c r="K98" s="6">
-        <v>2330</v>
+      <c r="R34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S34" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="V34" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="W34" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="X34" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="Y34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z34" s="1">
+        <v>5</v>
+      </c>
+      <c r="AB34" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="AF34" s="9" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="35" spans="1:32" s="1" customFormat="1">
+      <c r="A35" s="1">
+        <v>32</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E35" s="1">
+        <v>48000</v>
+      </c>
+      <c r="G35" s="1">
+        <v>24000</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="O35" s="1">
+        <v>10</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="V35" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="W35" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="X35" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="Y35" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z35" s="1">
+        <v>5</v>
+      </c>
+      <c r="AB35" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="AF35" s="9" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="99" spans="11:13">
@@ -4335,9 +4508,9 @@
       <c r="M99" s="5"/>
     </row>
     <row r="100" spans="11:13">
-      <c r="K100" s="5"/>
-      <c r="L100" s="5"/>
-      <c r="M100" s="5"/>
+      <c r="K100" s="6">
+        <v>2330</v>
+      </c>
     </row>
     <row r="101" spans="11:13">
       <c r="K101" s="5"/>
@@ -4598,6 +4771,16 @@
       <c r="K152" s="5"/>
       <c r="L152" s="5"/>
       <c r="M152" s="5"/>
+    </row>
+    <row r="153" spans="11:13">
+      <c r="K153" s="5"/>
+      <c r="L153" s="5"/>
+      <c r="M153" s="5"/>
+    </row>
+    <row r="154" spans="11:13">
+      <c r="K154" s="5"/>
+      <c r="L154" s="5"/>
+      <c r="M154" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -4612,45 +4795,49 @@
     <hyperlink ref="W7" r:id="rId8" xr:uid="{629D8B59-FF64-D34B-A220-1E6FAD75B946}"/>
     <hyperlink ref="X7" r:id="rId9" xr:uid="{150A683E-B1F2-3D44-A4B1-8027CE2811E4}"/>
     <hyperlink ref="W8" r:id="rId10" xr:uid="{C5FC9B63-9275-0241-9524-5B9A5EACC3B4}"/>
-    <hyperlink ref="W9" r:id="rId11" xr:uid="{7FE9CA90-1EE3-AD40-881F-D893DB76F37C}"/>
-    <hyperlink ref="X9" r:id="rId12" xr:uid="{3E0979AD-6FC5-8D4B-8DA4-8A4E897123A2}"/>
-    <hyperlink ref="W10" r:id="rId13" xr:uid="{F4305473-D7A1-1145-B9D5-6EFF98079711}"/>
-    <hyperlink ref="W12" r:id="rId14" xr:uid="{959160A2-10D5-2448-A439-CDBFF4F0F9F1}"/>
-    <hyperlink ref="W11" r:id="rId15" xr:uid="{207C94FC-8117-5E4F-BB27-41252E25866C}"/>
-    <hyperlink ref="W13" r:id="rId16" xr:uid="{DF9E0F33-C6D1-2E4F-8FF2-0A1705E030DE}"/>
-    <hyperlink ref="X14" r:id="rId17" xr:uid="{F1A09BDD-725A-4F40-A5BB-83D9A61C3867}"/>
-    <hyperlink ref="W14" r:id="rId18" xr:uid="{1B87D0CF-5CD0-954A-A37C-8D172022C386}"/>
-    <hyperlink ref="X15" r:id="rId19" xr:uid="{FA878428-ADB6-D841-9B6C-CCD2DBAA54F4}"/>
-    <hyperlink ref="W15" r:id="rId20" xr:uid="{67FC3E2A-C59C-3746-803A-57944543536D}"/>
-    <hyperlink ref="W16" r:id="rId21" xr:uid="{7F20631E-9A9A-644C-9C2F-7A7610CE04A0}"/>
-    <hyperlink ref="W17" r:id="rId22" xr:uid="{D17AB5E2-B797-BA44-ACBD-E585141F1571}"/>
-    <hyperlink ref="W18" r:id="rId23" xr:uid="{788461B1-8AB5-A342-88A2-9CB73D7EC39E}"/>
-    <hyperlink ref="X16" r:id="rId24" xr:uid="{28267EC8-F4EE-5D4C-8311-C9313455F82A}"/>
-    <hyperlink ref="X18" r:id="rId25" xr:uid="{974C8335-85B8-7A49-9F0C-16E3528E1D9E}"/>
-    <hyperlink ref="X17" r:id="rId26" xr:uid="{D163CB0A-1F89-184C-8EC1-1669E3255569}"/>
-    <hyperlink ref="X19" r:id="rId27" xr:uid="{D8B4F5BE-4364-4244-8F9E-18AF83F5D35A}"/>
-    <hyperlink ref="W19" r:id="rId28" xr:uid="{3E0A8D53-DC59-F844-BD82-7E678F2FAF43}"/>
-    <hyperlink ref="W20" r:id="rId29" xr:uid="{738D47FD-7AA8-2A44-BA0C-6C2CB665A9C9}"/>
-    <hyperlink ref="W21" r:id="rId30" xr:uid="{DF8CAA92-BE10-A140-9843-3E7E73E2DD11}"/>
-    <hyperlink ref="W22" r:id="rId31" xr:uid="{0AA240D4-EFDD-8449-BE97-588925472974}"/>
-    <hyperlink ref="W23" r:id="rId32" xr:uid="{F64D1BE3-B2E9-EF44-ACC4-D1EC217814EA}"/>
-    <hyperlink ref="X23" r:id="rId33" xr:uid="{E5FC0BAB-0993-1C49-97EE-CB0BB5B6364D}"/>
-    <hyperlink ref="W24" r:id="rId34" xr:uid="{DCB8E592-60A3-2844-9186-4F23C17F860F}"/>
-    <hyperlink ref="W29" r:id="rId35" location="hanamomo" xr:uid="{19F8746F-FD67-C745-9C79-CFF8930D335A}"/>
-    <hyperlink ref="W28" r:id="rId36" location="spa" xr:uid="{3F3BB9C6-4A38-8B49-9251-2484D4310862}"/>
-    <hyperlink ref="W25" r:id="rId37" xr:uid="{C65AB0CE-08FE-9C47-B1AE-67CDCC7EDA9B}"/>
-    <hyperlink ref="W26" r:id="rId38" xr:uid="{6D455A41-F025-C945-8451-21A5DFEFE851}"/>
-    <hyperlink ref="W30" r:id="rId39" xr:uid="{7D46792A-1672-F74C-B0EC-DA6078040105}"/>
-    <hyperlink ref="W31" r:id="rId40" xr:uid="{CF120394-0FD4-7A44-9A27-967B61797B9C}"/>
-    <hyperlink ref="W32" r:id="rId41" xr:uid="{1F279012-82DB-6F46-9DB9-4B028EE0E3CC}"/>
-    <hyperlink ref="W33" r:id="rId42" xr:uid="{9EDAA3EF-F3B4-1348-9D76-10657DBA2346}"/>
-    <hyperlink ref="X32" r:id="rId43" xr:uid="{09ADA551-99DA-D54C-B8B7-BF142CC34F75}"/>
-    <hyperlink ref="X33" r:id="rId44" xr:uid="{7F239BD4-7947-344C-9D1E-AC44897B99FA}"/>
+    <hyperlink ref="W11" r:id="rId11" xr:uid="{7FE9CA90-1EE3-AD40-881F-D893DB76F37C}"/>
+    <hyperlink ref="X11" r:id="rId12" xr:uid="{3E0979AD-6FC5-8D4B-8DA4-8A4E897123A2}"/>
+    <hyperlink ref="W12" r:id="rId13" xr:uid="{F4305473-D7A1-1145-B9D5-6EFF98079711}"/>
+    <hyperlink ref="W14" r:id="rId14" xr:uid="{959160A2-10D5-2448-A439-CDBFF4F0F9F1}"/>
+    <hyperlink ref="W13" r:id="rId15" xr:uid="{207C94FC-8117-5E4F-BB27-41252E25866C}"/>
+    <hyperlink ref="W15" r:id="rId16" xr:uid="{DF9E0F33-C6D1-2E4F-8FF2-0A1705E030DE}"/>
+    <hyperlink ref="X16" r:id="rId17" xr:uid="{F1A09BDD-725A-4F40-A5BB-83D9A61C3867}"/>
+    <hyperlink ref="W16" r:id="rId18" xr:uid="{1B87D0CF-5CD0-954A-A37C-8D172022C386}"/>
+    <hyperlink ref="X17" r:id="rId19" xr:uid="{FA878428-ADB6-D841-9B6C-CCD2DBAA54F4}"/>
+    <hyperlink ref="W17" r:id="rId20" xr:uid="{67FC3E2A-C59C-3746-803A-57944543536D}"/>
+    <hyperlink ref="W18" r:id="rId21" xr:uid="{7F20631E-9A9A-644C-9C2F-7A7610CE04A0}"/>
+    <hyperlink ref="W19" r:id="rId22" xr:uid="{D17AB5E2-B797-BA44-ACBD-E585141F1571}"/>
+    <hyperlink ref="W20" r:id="rId23" xr:uid="{788461B1-8AB5-A342-88A2-9CB73D7EC39E}"/>
+    <hyperlink ref="X18" r:id="rId24" xr:uid="{28267EC8-F4EE-5D4C-8311-C9313455F82A}"/>
+    <hyperlink ref="X20" r:id="rId25" xr:uid="{974C8335-85B8-7A49-9F0C-16E3528E1D9E}"/>
+    <hyperlink ref="X19" r:id="rId26" xr:uid="{D163CB0A-1F89-184C-8EC1-1669E3255569}"/>
+    <hyperlink ref="X21" r:id="rId27" xr:uid="{D8B4F5BE-4364-4244-8F9E-18AF83F5D35A}"/>
+    <hyperlink ref="W21" r:id="rId28" xr:uid="{3E0A8D53-DC59-F844-BD82-7E678F2FAF43}"/>
+    <hyperlink ref="W22" r:id="rId29" xr:uid="{738D47FD-7AA8-2A44-BA0C-6C2CB665A9C9}"/>
+    <hyperlink ref="W23" r:id="rId30" xr:uid="{DF8CAA92-BE10-A140-9843-3E7E73E2DD11}"/>
+    <hyperlink ref="W24" r:id="rId31" xr:uid="{0AA240D4-EFDD-8449-BE97-588925472974}"/>
+    <hyperlink ref="W25" r:id="rId32" xr:uid="{F64D1BE3-B2E9-EF44-ACC4-D1EC217814EA}"/>
+    <hyperlink ref="X25" r:id="rId33" xr:uid="{E5FC0BAB-0993-1C49-97EE-CB0BB5B6364D}"/>
+    <hyperlink ref="W26" r:id="rId34" xr:uid="{DCB8E592-60A3-2844-9186-4F23C17F860F}"/>
+    <hyperlink ref="W31" r:id="rId35" location="hanamomo" xr:uid="{19F8746F-FD67-C745-9C79-CFF8930D335A}"/>
+    <hyperlink ref="W30" r:id="rId36" location="spa" xr:uid="{3F3BB9C6-4A38-8B49-9251-2484D4310862}"/>
+    <hyperlink ref="W27" r:id="rId37" xr:uid="{C65AB0CE-08FE-9C47-B1AE-67CDCC7EDA9B}"/>
+    <hyperlink ref="W28" r:id="rId38" xr:uid="{6D455A41-F025-C945-8451-21A5DFEFE851}"/>
+    <hyperlink ref="W32" r:id="rId39" xr:uid="{7D46792A-1672-F74C-B0EC-DA6078040105}"/>
+    <hyperlink ref="W33" r:id="rId40" xr:uid="{CF120394-0FD4-7A44-9A27-967B61797B9C}"/>
+    <hyperlink ref="W34" r:id="rId41" xr:uid="{1F279012-82DB-6F46-9DB9-4B028EE0E3CC}"/>
+    <hyperlink ref="W35" r:id="rId42" xr:uid="{9EDAA3EF-F3B4-1348-9D76-10657DBA2346}"/>
+    <hyperlink ref="X34" r:id="rId43" xr:uid="{09ADA551-99DA-D54C-B8B7-BF142CC34F75}"/>
+    <hyperlink ref="X35" r:id="rId44" xr:uid="{7F239BD4-7947-344C-9D1E-AC44897B99FA}"/>
+    <hyperlink ref="W10" r:id="rId45" xr:uid="{38D6470F-8C87-FD42-88A6-5E73E94F24D4}"/>
+    <hyperlink ref="X10" r:id="rId46" xr:uid="{C8700646-BA74-8B45-AA21-314ED7EF76EA}"/>
+    <hyperlink ref="W9" r:id="rId47" xr:uid="{CE65D3E5-8876-024C-8EFE-9BE4E1E20DDD}"/>
+    <hyperlink ref="X9" r:id="rId48" xr:uid="{1F528120-5702-F24A-9024-464535C70995}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <ignoredErrors>
-    <ignoredError sqref="O1:AA1 A1:C1 B27 B13 G8 G23:G25 G9:G11 H1:H3 H26:H31 H8 H23:H25 F1:G3 F26:G27 P11:R11 O2:R2 T2:U2 X2:AA2 P19:R19 P12:R12 X12:Y12 O3:R3 X3:Y3 T3:U3 P4:Q4 T4:V4 X4:Y4 P5:Q5 T5:V5 Y5 P6:R6 Y6 B6 H4:H7 F4:G7 P7:R7 Y7:AA7 T6:U6 U7:V7 E8 P8:Q8 U8:V8 X8:Y8 P9:R9 U9 Y9:AA9 B9 E9 B10 E10 O10:R10 U10 U11:V11 E11 U12 P13:Q13 U13:V13 B25 E14 P14:Q14 U14:V14 E7 X10:AA10 G13:G21 X11:Y11 E13 P21:Q21 P20:Q20 T20:U20 O31:R31 P23:Q23 T23:V23 X13:Z13 Y14 O15:R15 T15:V15 P17:Q17 T18:V18 P18 Y15:AA15 B15 E15 B16 E16 B17 E17 B18 E18 U16:V16 Y16:Z16 T17:V17 Y17:Z17 Y18:Z18 Y19 T19:V19 B19 E19 Y20 B20 E20 B21 E21 T21:V21 X21 B23 E23 P24:R24 X24:AA24 T24:V24 P25:R25 T27:Y27 O30:R30 T30:V30 T31:V31 B24 E24 T29:V29 X29:AA29 B31 B28 T28:V28 X28:Y28 F29:G31 F28 T25:V25 X25:Z25 T26:V26 X26:Z26 B26 E26 P28:R29 P26:Q26 E27 X30:AA30 X31:AA31 AA3 AA11 AA12 AA28 AA27 AA21 A3:B3 A2:B2 E2 E25 B29 E29 B30 E30 E31 E3 B4 E4 B5 E5 E6 E1 P27:R27 P16:Q16" numberStoredAsText="1"/>
+    <ignoredError sqref="O1:AA1 A1:C1 B29 B15 G8 G25:G27 G12:G13 H1:H3 H28:H33 H8 H25:H27 F1:G3 F28:G29 P13:R13 O2:R2 T2:U2 X2:AA2 P21:R21 P14:R14 X14:Y14 O3:R3 X3:Y3 T3:U3 P4:Q4 T4:V4 X4:Y4 P5:Q5 T5:V5 Y5 P6:R6 Y6 B6 H4:H7 F4:G7 P7:R7 Y7:AA7 T6:U6 U7:V7 E8 P8:Q8 U8:V8 X8:Y8 P11:R11 U11 Y11:AA11 B12 E12 O12:R12 U12 U13:V13 E13 U14 P15:Q15 U15:V15 B27 E16 P16:Q16 U16:V16 E7 X12:AA12 G15:G23 X13:Y13 E15 P23:Q23 P22:Q22 T22:U22 O33:R33 P25:Q25 T25:V25 X15:Z15 Y16 O17:R17 T17:V17 P19:Q19 T20:V20 P20 Y17:AA17 B17 E17 B18 E18 B19 E19 B20 E20 U18:V18 Y18:Z18 T19:V19 Y19:Z19 Y20:Z20 Y21 T21:V21 B21 E21 Y22 B22 E22 B23 E23 T23:V23 X23 B25 E25 P26:R26 X26:AA26 T26:V26 P27:R27 T29:Y29 O32:R32 T32:V32 T33:V33 B26 E26 T31:V31 X31:AA31 B33 B30 T30:V30 X30:Y30 F31:G33 F30 T27:V27 X27:Z27 T28:V28 X28:Z28 B28 E28 P30:R31 P28:Q28 E29 X32:AA32 X33:AA33 AA3 AA13 AA14 AA30 AA29 AA23 A3:B3 A2:B2 E2 E27 B31 E31 B32 E32 E33 E3 B4 E4 B5 E5 E6 E1 P29:R29 P18:Q18" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>